--- a/artfynd/A 51629-2024 artfynd.xlsx
+++ b/artfynd/A 51629-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>4242198</v>
       </c>
       <c r="B2" t="n">
-        <v>95521</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>413091.1788408556</v>
+        <v>413091</v>
       </c>
       <c r="R2" t="n">
-        <v>6371018.652512703</v>
+        <v>6371019</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1995-06-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1995-06-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 51629-2024 artfynd.xlsx
+++ b/artfynd/A 51629-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242198</v>
       </c>
       <c r="B2" t="n">
-        <v>97451</v>
+        <v>97457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51629-2024 artfynd.xlsx
+++ b/artfynd/A 51629-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242198</v>
       </c>
       <c r="B2" t="n">
-        <v>97457</v>
+        <v>97463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51629-2024 artfynd.xlsx
+++ b/artfynd/A 51629-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242198</v>
       </c>
       <c r="B2" t="n">
-        <v>97463</v>
+        <v>97465</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51629-2024 artfynd.xlsx
+++ b/artfynd/A 51629-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242198</v>
       </c>
       <c r="B2" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51629-2024 artfynd.xlsx
+++ b/artfynd/A 51629-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242198</v>
       </c>
       <c r="B2" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51629-2024 artfynd.xlsx
+++ b/artfynd/A 51629-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242198</v>
       </c>
       <c r="B2" t="n">
-        <v>97493</v>
+        <v>97499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51629-2024 artfynd.xlsx
+++ b/artfynd/A 51629-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242198</v>
       </c>
       <c r="B2" t="n">
-        <v>97499</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51629-2024 artfynd.xlsx
+++ b/artfynd/A 51629-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242198</v>
       </c>
       <c r="B2" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51629-2024 artfynd.xlsx
+++ b/artfynd/A 51629-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242198</v>
       </c>
       <c r="B2" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
